--- a/data/trans_orig/P43A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43A-Estudios-trans_orig.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,25 +526,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última mamografía que le hicieron en 2007</t>
+          <t>Población según el tiempo transcurrido desde la última mamografía que le hicieron en 2007 (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +548,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -564,17 +557,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -645,41 +627,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -702,13 +649,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -723,37 +663,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>175</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176250</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>199975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153434</t>
+          <t>154070</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>198466</t>
+          <t>199975</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,47 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>176250</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>153434</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>198466</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>28,5%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>32,09%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -836,37 +741,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>222</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221532</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>198993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198356</t>
+          <t>198993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245324</t>
+          <t>244995</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>221532</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>198356</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>245324</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>35,82%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>32,07%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>39,66%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -949,37 +819,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>129</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>124415</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106082</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145450</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>104981</t>
+          <t>106082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144243</t>
+          <t>145450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,47 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>124415</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>104981</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>144243</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>20,12%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>16,97%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>23,32%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -1062,37 +897,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96301</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79906</t>
+          <t>80978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114583</t>
+          <t>113439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,47 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>79906</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>114583</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>12,92%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>18,53%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -1175,37 +975,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>622</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>618499</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>618499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>618499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1239,41 +1039,6 @@
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>618499</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>618499</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>618499</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1292,37 +1057,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101888</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84544</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121513</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84073</t>
+          <t>84544</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124315</t>
+          <t>121513</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,47 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>101888</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>84073</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>124315</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>21,2%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>17,49%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -1405,37 +1135,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>165</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>167654</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147373</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>190275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147192</t>
+          <t>147373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190846</t>
+          <t>190275</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,47 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>167654</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>147192</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>190846</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>30,62%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>39,7%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -1518,37 +1213,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>124</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>127219</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108284</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>147935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>106881</t>
+          <t>108284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146173</t>
+          <t>147935</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,47 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>127219</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>106881</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>146173</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>30,41%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -1631,37 +1291,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83948</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101560</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67748</t>
+          <t>67837</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101023</t>
+          <t>101560</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,47 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>83948</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>67748</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>101023</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>17,46%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>21,02%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -1744,37 +1369,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>464</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480709</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1808,41 +1433,6 @@
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>480709</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>480709</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>480709</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1861,37 +1451,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17420</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36488</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,47 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>26010</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>17420</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>36488</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>21,68%</t>
+          <t>21,54%</t>
         </is>
       </c>
     </row>
@@ -1974,37 +1529,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59135</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47875</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72454</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47226</t>
+          <t>47875</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71564</t>
+          <t>72454</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,47 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>59135</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>47226</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>71564</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>28,06%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>42,53%</t>
+          <t>43,05%</t>
         </is>
       </c>
     </row>
@@ -2087,37 +1607,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43654</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56818</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>33503</t>
+          <t>32996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55851</t>
+          <t>56818</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,47 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>43654</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>33503</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>55851</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>33,19%</t>
+          <t>33,76%</t>
         </is>
       </c>
     </row>
@@ -2200,37 +1685,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39486</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51823</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28830</t>
+          <t>28409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>50596</t>
+          <t>51823</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,47 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>39486</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>28830</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>50596</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>23,46%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>30,07%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -2313,37 +1763,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168286</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168286</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168286</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2377,41 +1827,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>168286</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>168286</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>168286</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2430,37 +1845,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>294</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304148</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>272176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>337318</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275360</t>
+          <t>272176</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>335228</t>
+          <t>337318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,47 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>304148</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>275360</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>335228</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>24,0%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -2543,37 +1923,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>442</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>448321</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>486761</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>417372</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>482055</t>
+          <t>486761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,47 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>448321</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>417372</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>482055</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>32,93%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -2656,37 +2001,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>295</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>295289</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266117</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325962</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>266854</t>
+          <t>266117</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>323641</t>
+          <t>325962</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,47 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>295289</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>266854</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>323641</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>23,3%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>21,05%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>25,53%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -2769,37 +2079,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>219736</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195365</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249938</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193924</t>
+          <t>195365</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>248021</t>
+          <t>249938</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,47 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>219736</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>193924</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>248021</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -2882,37 +2157,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1267494</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1267494</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1267494</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2946,41 +2221,6 @@
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1246</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1267494</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1267494</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1267494</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2994,13 +2234,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="C1:I1"/>
   </mergeCells>
@@ -3014,7 +2253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3033,25 +2272,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última mamografía que le hicieron en 2012</t>
+          <t>Población según el tiempo transcurrido desde la última mamografía que le hicieron en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3062,7 +2294,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3071,17 +2303,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3152,41 +2373,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3209,13 +2395,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3230,37 +2409,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220454</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195502</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +2454,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195708</t>
+          <t>195502</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>248006</t>
+          <t>248700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,47 +2469,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>220454</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>195708</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>248006</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>25,97%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>29,22%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -3343,37 +2487,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>309</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>329399</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>297974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>355099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +2532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301160</t>
+          <t>297974</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>358308</t>
+          <t>355099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,47 +2547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>329399</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>301160</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>358308</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>38,81%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>35,48%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>42,21%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -3456,37 +2565,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170196</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221424</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +2610,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>169914</t>
+          <t>170196</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218847</t>
+          <t>221424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,47 +2625,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>195119</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>169914</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>218847</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>22,99%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>25,78%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -3569,37 +2643,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103876</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84987</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>122730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +2688,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87558</t>
+          <t>84987</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126577</t>
+          <t>122730</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,47 +2703,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>103876</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>87558</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>126577</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -3682,37 +2721,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>795</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>848848</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>848848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>848848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3746,41 +2785,6 @@
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>848848</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>848848</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>848848</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3799,37 +2803,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98399</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>80194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119410</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +2848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81249</t>
+          <t>80194</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>122060</t>
+          <t>119410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,47 +2863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>98399</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>81249</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>122060</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>18,68%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -3912,37 +2881,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>224</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247837</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275543</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +2926,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>219750</t>
+          <t>221841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272792</t>
+          <t>275543</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,47 +2941,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>247837</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>219750</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>272792</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>37,92%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>33,62%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>41,74%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -4025,37 +2959,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>185</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>198550</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +3004,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176269</t>
+          <t>173363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>223958</t>
+          <t>222960</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,47 +3019,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>198550</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>176269</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>223958</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>30,38%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>26,97%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>34,27%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -4138,37 +3037,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108788</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>132805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +3082,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88615</t>
+          <t>89876</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>128352</t>
+          <t>132805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,47 +3097,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>108788</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>88615</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>128352</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>16,65%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>19,64%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -4251,37 +3115,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>589</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>653574</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>653574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>653574</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4315,41 +3179,6 @@
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>653574</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>653574</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>653574</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4368,37 +3197,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21055</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +3242,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32952</t>
+          <t>31770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,47 +3257,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>21055</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>13038</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>32952</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>20,66%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -4481,37 +3275,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59918</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75217</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +3320,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46648</t>
+          <t>47689</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73926</t>
+          <t>75217</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,47 +3335,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>59918</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>46648</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>73926</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>37,56%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>29,24%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>46,34%</t>
+          <t>47,15%</t>
         </is>
       </c>
     </row>
@@ -4594,37 +3353,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49782</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36784</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62717</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +3398,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37181</t>
+          <t>36784</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63473</t>
+          <t>62717</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,47 +3413,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>49782</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>37181</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>63473</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>31,2%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>23,31%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>39,79%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -4707,37 +3431,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +3476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>19553</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39825</t>
+          <t>40238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,47 +3491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>28779</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>20433</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>39825</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>24,96%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -4820,37 +3509,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>134</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159533</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159533</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4884,41 +3573,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>159533</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>159533</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>159533</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4937,37 +3591,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>310</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339907</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305633</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>376051</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +3636,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>304538</t>
+          <t>305633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>373242</t>
+          <t>376051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,47 +3651,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>339907</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>304538</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>373242</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>20,45%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>18,32%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>22,46%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -5050,37 +3669,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>583</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>637154</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>597289</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>684318</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +3714,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>597136</t>
+          <t>597289</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>679765</t>
+          <t>684318</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,47 +3729,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>637154</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>597136</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>679765</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>38,34%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>35,93%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>40,9%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -5163,37 +3747,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>408</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>443451</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>406510</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>480306</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +3792,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>408245</t>
+          <t>406510</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>478057</t>
+          <t>480306</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,47 +3807,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>443451</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>408245</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>478057</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>26,68%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>24,56%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -5276,37 +3825,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241443</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273040</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +3870,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>211962</t>
+          <t>213042</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272965</t>
+          <t>273040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,47 +3885,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>241443</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>211962</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>272965</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -5389,37 +3903,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1661955</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1661955</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1661955</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5453,41 +3967,6 @@
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1518</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1661955</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1661955</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1661955</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5501,13 +3980,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="C1:I1"/>
   </mergeCells>
@@ -5521,7 +3999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5540,25 +4018,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última mamografía que le hicieron en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última mamografía que le hicieron en 2016 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5569,7 +4040,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5578,17 +4049,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -5659,41 +4119,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -5716,13 +4141,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -5737,37 +4155,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>213</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247413</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +4200,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222552</t>
+          <t>222632</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>271976</t>
+          <t>273272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,47 +4215,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>247413</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>222552</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>271976</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>38,45%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>34,59%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>42,27%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -5850,37 +4233,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>206</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227054</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>251280</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +4278,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200644</t>
+          <t>202725</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>254578</t>
+          <t>251280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,47 +4293,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>227054</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>200644</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>254578</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>35,29%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>31,18%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>39,57%</t>
+          <t>39,05%</t>
         </is>
       </c>
     </row>
@@ -5963,37 +4311,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112106</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133151</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +4356,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94621</t>
+          <t>94373</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133908</t>
+          <t>133151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,47 +4371,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>112106</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>94621</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>133908</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>14,71%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>20,81%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -6076,37 +4389,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56849</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42796</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72100</t>
+          <t>72688</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,47 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>56849</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>42796</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>72100</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -6189,37 +4467,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>576</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643422</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643422</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643422</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6253,41 +4531,6 @@
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>643422</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>643422</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>643422</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6306,37 +4549,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>133</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126320</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173277</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +4594,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126601</t>
+          <t>126320</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>171754</t>
+          <t>173277</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,47 +4609,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>148478</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>126601</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>171754</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>17,32%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>20,04%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -6419,37 +4627,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>348</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>379133</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>408261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +4672,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>351428</t>
+          <t>348546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>412171</t>
+          <t>408261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,47 +4687,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>379133</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>351428</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>412171</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>44,24%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
+          <t>47,64%</t>
         </is>
       </c>
     </row>
@@ -6532,37 +4705,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213459</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +4750,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188819</t>
+          <t>187397</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241977</t>
+          <t>241554</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,47 +4765,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>213459</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>188819</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>241977</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>24,91%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -6645,37 +4783,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115976</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97270</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138808</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +4828,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98130</t>
+          <t>97270</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>137004</t>
+          <t>138808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,47 +4843,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>115976</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>98130</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>137004</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>11,45%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -6758,37 +4861,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>784</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>857045</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>857045</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>857045</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6822,41 +4925,6 @@
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>857045</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>857045</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>857045</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6875,37 +4943,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33100</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +4988,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>23420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45558</t>
+          <t>45822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,47 +5003,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>33100</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>23294</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>45558</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -6988,37 +5021,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96421</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81534</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115494</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +5066,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81381</t>
+          <t>81534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>113729</t>
+          <t>115494</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,47 +5081,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>96421</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>81381</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>113729</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>38,83%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>45,8%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -7101,37 +5099,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84801</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69282</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +5144,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69918</t>
+          <t>69282</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101599</t>
+          <t>102229</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,47 +5159,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>84801</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>69918</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>101599</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>34,15%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>40,92%</t>
+          <t>41,17%</t>
         </is>
       </c>
     </row>
@@ -7214,37 +5177,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33975</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +5222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23463</t>
+          <t>23531</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,47 +5237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>33975</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>23463</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>47812</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>9,45%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>19,26%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -7327,37 +5255,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>227</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248297</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248297</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248297</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7391,41 +5319,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>248297</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>248297</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>248297</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7444,37 +5337,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>376</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>428991</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>393797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>469540</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +5382,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>392971</t>
+          <t>393797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>467829</t>
+          <t>469540</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,47 +5397,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>428991</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>392971</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>467829</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>24,53%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>22,47%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>26,75%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -7557,37 +5415,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>644</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>702608</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>660923</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>742855</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +5460,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>663015</t>
+          <t>660923</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>748992</t>
+          <t>742855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,47 +5475,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>702608</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>663015</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>748992</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>40,18%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>37,91%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>42,83%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -7670,37 +5493,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>378</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410366</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>378870</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>454823</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +5538,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>369721</t>
+          <t>378870</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>446126</t>
+          <t>454823</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,47 +5553,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>410366</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>369721</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>446126</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>23,47%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>21,14%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>25,51%</t>
+          <t>26,01%</t>
         </is>
       </c>
     </row>
@@ -7783,37 +5571,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>189</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206799</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>235930</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +5616,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>180792</t>
+          <t>181042</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>236323</t>
+          <t>235930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,47 +5631,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>206799</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>180792</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>236323</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -7896,37 +5649,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1587</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1748764</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1748764</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1748764</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7960,41 +5713,6 @@
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1748764</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1748764</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1748764</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8008,13 +5726,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="C1:I1"/>
   </mergeCells>
@@ -8028,7 +5745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8047,25 +5764,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última mamografía que le hicieron en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última mamografía que le hicieron en 2023 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8076,7 +5786,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8085,17 +5795,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -8166,41 +5865,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -8223,13 +5887,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -8244,37 +5901,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>456</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>218835</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>205051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>232559</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +5946,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>204249</t>
+          <t>205051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230817</t>
+          <t>232559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,47 +5961,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>218835</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>204249</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>230817</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>55,26%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>51,57%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>58,28%</t>
+          <t>58,72%</t>
         </is>
       </c>
     </row>
@@ -8357,37 +5979,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>191</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>99706</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113128</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +6024,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87671</t>
+          <t>87978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113588</t>
+          <t>113128</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,47 +6039,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>99706</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>87671</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>113588</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>25,18%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>28,68%</t>
+          <t>28,57%</t>
         </is>
       </c>
     </row>
@@ -8470,37 +6057,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53394</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +6102,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45152</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65319</t>
+          <t>63389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,47 +6117,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>53394</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>45152</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>65319</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>16,49%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -8583,37 +6135,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24090</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18246</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +6180,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>18246</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>32097</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,47 +6195,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>24090</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>17693</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>31926</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -8696,37 +6213,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>789</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>396025</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>396025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>396025</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,41 +6277,6 @@
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>789</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>396025</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>396025</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>396025</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8813,37 +6295,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>311</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206164</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104670</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>287035</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +6340,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98520</t>
+          <t>104670</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>294051</t>
+          <t>287035</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,47 +6355,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>206164</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>98520</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>294051</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>32,25%</t>
+          <t>31,48%</t>
         </is>
       </c>
     </row>
@@ -8926,37 +6373,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>415</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>433220</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>284786</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>658121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +6418,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>282748</t>
+          <t>284786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>653480</t>
+          <t>658121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,47 +6433,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>433220</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>282748</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>653480</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>47,52%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>31,01%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>71,68%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -9039,37 +6451,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>173244</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>233893</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +6496,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>93955</t>
+          <t>94599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>233256</t>
+          <t>233893</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,47 +6511,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>173244</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>93955</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>233256</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>25,58%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -9152,37 +6529,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>166</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>99084</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +6574,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>50890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134565</t>
+          <t>136645</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,47 +6589,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>99084</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>51113</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>134565</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>14,76%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -9265,37 +6607,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>911712</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>911712</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>911712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,41 +6671,6 @@
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1195</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>911712</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>911712</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>911712</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9382,37 +6689,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>96</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54335</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66287</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +6734,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44962</t>
+          <t>44855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66297</t>
+          <t>66287</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,45 +6749,10 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>54335</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>44962</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>66297</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>20,29%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>24,76%</t>
         </is>
@@ -9495,37 +6767,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>87639</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76006</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>101217</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +6812,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>74956</t>
+          <t>76006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>99675</t>
+          <t>101217</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,47 +6827,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>87639</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>74956</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>99675</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>32,73%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>27,99%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>37,22%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -9608,37 +6845,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>147</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82476</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>94291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +6890,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70166</t>
+          <t>70165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95127</t>
+          <t>94291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9673,42 +6910,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>82476</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>70166</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>95127</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>30,8%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>26,2%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>35,53%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -9721,37 +6923,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43322</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55485</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +6968,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33492</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>55485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,47 +6983,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>43322</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>33492</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>53645</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
+          <t>20,72%</t>
         </is>
       </c>
     </row>
@@ -9834,37 +7001,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>470</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267772</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267772</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267772</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,41 +7065,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>267772</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>267772</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>267772</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9951,37 +7083,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>863</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>479333</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304420</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>570506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +7128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>315330</t>
+          <t>304420</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>570941</t>
+          <t>570506</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,47 +7143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>479333</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>315330</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>570941</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>30,42%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>20,01%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>36,24%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -10064,37 +7161,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>765</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>620565</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>464730</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>959931</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +7206,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>467364</t>
+          <t>464730</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>939739</t>
+          <t>959931</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,47 +7221,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>620565</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>467364</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>939739</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>39,39%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>29,66%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>59,65%</t>
+          <t>60,93%</t>
         </is>
       </c>
     </row>
@@ -10177,37 +7239,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>547</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>309114</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>199074</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>366868</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +7284,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>208623</t>
+          <t>199074</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>368626</t>
+          <t>366868</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,47 +7299,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>309114</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>208623</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>368626</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>23,4%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -10290,37 +7317,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>279</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166496</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>107739</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>201093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +7362,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>109886</t>
+          <t>107739</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200585</t>
+          <t>201093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,47 +7377,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>166496</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>109886</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>200585</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -10403,37 +7395,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1575509</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1575509</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1575509</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10467,41 +7459,6 @@
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1575509</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1575509</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1575509</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10515,13 +7472,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A9:A13"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A19:A23"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="C1:I1"/>
   </mergeCells>

--- a/data/trans_orig/P43A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P43A-Estudios-trans_orig.xlsx
@@ -673,12 +673,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154070</t>
+          <t>156078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>199975</t>
+          <t>199598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -688,12 +688,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>154070</t>
+          <t>156078</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>199975</t>
+          <t>199598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>198683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244995</t>
+          <t>243215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>198993</t>
+          <t>198683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244995</t>
+          <t>243215</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106082</t>
+          <t>105720</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>145450</t>
+          <t>145166</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>106082</t>
+          <t>105720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>145450</t>
+          <t>145166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80978</t>
+          <t>79204</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113439</t>
+          <t>113990</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80978</t>
+          <t>79204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113439</t>
+          <t>113990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84544</t>
+          <t>86593</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121513</t>
+          <t>121357</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84544</t>
+          <t>86593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>121513</t>
+          <t>121357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147373</t>
+          <t>146593</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190275</t>
+          <t>188264</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1180,12 +1180,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>147373</t>
+          <t>146593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>190275</t>
+          <t>188264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108284</t>
+          <t>110314</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147935</t>
+          <t>148746</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108284</t>
+          <t>110314</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147935</t>
+          <t>148746</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67837</t>
+          <t>68448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101560</t>
+          <t>101637</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67837</t>
+          <t>68448</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101560</t>
+          <t>101637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36255</t>
+          <t>35939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>17793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36255</t>
+          <t>35939</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47875</t>
+          <t>47331</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72454</t>
+          <t>71799</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47875</t>
+          <t>47331</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72454</t>
+          <t>71799</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,66%</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32996</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32996</t>
+          <t>33790</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -1695,12 +1695,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>29875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51823</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>29875</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>51823</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>272176</t>
+          <t>274444</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>337318</t>
+          <t>335864</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>414272</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>486761</t>
+          <t>481869</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,02%</t>
         </is>
       </c>
     </row>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>266117</t>
+          <t>266466</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>195365</t>
+          <t>195391</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249938</t>
+          <t>249488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -2419,12 +2419,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>195502</t>
+          <t>195229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>248700</t>
+          <t>247796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>195502</t>
+          <t>195229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>248700</t>
+          <t>247796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -2497,12 +2497,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>297974</t>
+          <t>301059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>355099</t>
+          <t>358436</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297974</t>
+          <t>301059</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>355099</t>
+          <t>358436</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -2575,12 +2575,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170196</t>
+          <t>171048</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221424</t>
+          <t>218153</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>170196</t>
+          <t>171048</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>221424</t>
+          <t>218153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -2653,12 +2653,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84987</t>
+          <t>87071</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122730</t>
+          <t>126641</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2688,12 +2688,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84987</t>
+          <t>87071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122730</t>
+          <t>126641</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -2813,12 +2813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80194</t>
+          <t>79694</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119410</t>
+          <t>119738</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80194</t>
+          <t>79694</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119410</t>
+          <t>119738</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,32%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>221841</t>
+          <t>222339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>275543</t>
+          <t>273135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>221841</t>
+          <t>222339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>275543</t>
+          <t>273135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -2969,12 +2969,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173363</t>
+          <t>175110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222960</t>
+          <t>224365</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173363</t>
+          <t>175110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>222960</t>
+          <t>224365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>89876</t>
+          <t>88165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>132805</t>
+          <t>129452</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89876</t>
+          <t>88165</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>132805</t>
+          <t>129452</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -3207,12 +3207,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31770</t>
+          <t>32868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>47893</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>75217</t>
+          <t>73558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47689</t>
+          <t>47893</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75217</t>
+          <t>73558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3335,12 +3335,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,11%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>36215</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62717</t>
+          <t>62235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36784</t>
+          <t>36215</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62717</t>
+          <t>62235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -3441,12 +3441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40238</t>
+          <t>40432</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3456,12 +3456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19553</t>
+          <t>19408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40238</t>
+          <t>40432</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>305633</t>
+          <t>308308</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>376051</t>
+          <t>378178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>305633</t>
+          <t>308308</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>376051</t>
+          <t>378178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,76%</t>
         </is>
       </c>
     </row>
@@ -3679,12 +3679,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>597289</t>
+          <t>593444</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>684318</t>
+          <t>676511</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>597289</t>
+          <t>593444</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>684318</t>
+          <t>676511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -3757,12 +3757,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>406510</t>
+          <t>408301</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>480306</t>
+          <t>480170</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>406510</t>
+          <t>408301</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>480306</t>
+          <t>480170</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -3835,12 +3835,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>213042</t>
+          <t>212242</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>273040</t>
+          <t>275986</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>213042</t>
+          <t>212242</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>273040</t>
+          <t>275986</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>222632</t>
+          <t>223190</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>273272</t>
+          <t>273513</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222632</t>
+          <t>223190</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273272</t>
+          <t>273513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,51%</t>
         </is>
       </c>
     </row>
@@ -4243,12 +4243,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>202725</t>
+          <t>200320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251280</t>
+          <t>251726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4258,12 +4258,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4278,12 +4278,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>202725</t>
+          <t>200320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>251280</t>
+          <t>251726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94373</t>
+          <t>93919</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>133151</t>
+          <t>135988</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>94373</t>
+          <t>93919</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133151</t>
+          <t>135988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43154</t>
+          <t>43737</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72688</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43154</t>
+          <t>43737</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72688</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4559,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126320</t>
+          <t>125640</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173277</t>
+          <t>172488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126320</t>
+          <t>125640</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>173277</t>
+          <t>172488</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -4637,12 +4637,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>348546</t>
+          <t>352614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>408261</t>
+          <t>410861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4652,12 +4652,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>348546</t>
+          <t>352614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>408261</t>
+          <t>410861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>187397</t>
+          <t>190097</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>241554</t>
+          <t>239244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187397</t>
+          <t>190097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>241554</t>
+          <t>239244</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>27,91%</t>
         </is>
       </c>
     </row>
@@ -4793,12 +4793,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97270</t>
+          <t>96801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>138808</t>
+          <t>136714</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97270</t>
+          <t>96801</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>138808</t>
+          <t>136714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45822</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4988,12 +4988,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23420</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45822</t>
+          <t>43981</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -5031,12 +5031,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81534</t>
+          <t>81709</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>115494</t>
+          <t>112532</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5046,12 +5046,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5066,12 +5066,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81534</t>
+          <t>81709</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>115494</t>
+          <t>112532</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -5109,12 +5109,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69282</t>
+          <t>70022</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102229</t>
+          <t>100892</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69282</t>
+          <t>70022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102229</t>
+          <t>100892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5159,12 +5159,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46433</t>
+          <t>46809</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23531</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46433</t>
+          <t>46809</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -5347,12 +5347,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>393797</t>
+          <t>388244</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>469540</t>
+          <t>465966</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>393797</t>
+          <t>388244</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>469540</t>
+          <t>465966</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>660923</t>
+          <t>661991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>742855</t>
+          <t>747567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>660923</t>
+          <t>661991</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>742855</t>
+          <t>747567</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,75%</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5503,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>378870</t>
+          <t>376454</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>454823</t>
+          <t>450821</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>378870</t>
+          <t>376454</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>454823</t>
+          <t>450821</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -5581,12 +5581,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>181042</t>
+          <t>181520</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>235930</t>
+          <t>237059</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>181042</t>
+          <t>181520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>235930</t>
+          <t>237059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -5906,32 +5906,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>218835</t>
+          <t>235427</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>205051</t>
+          <t>219983</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>232559</t>
+          <t>250831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5941,32 +5941,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>218835</t>
+          <t>235427</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205051</t>
+          <t>219983</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>232559</t>
+          <t>250831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -5984,32 +5984,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>99706</t>
+          <t>110067</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87978</t>
+          <t>97353</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113128</t>
+          <t>125378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6019,32 +6019,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>99706</t>
+          <t>110067</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87978</t>
+          <t>97353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113128</t>
+          <t>125378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -6062,32 +6062,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53394</t>
+          <t>57989</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>47888</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63389</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6097,32 +6097,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>53394</t>
+          <t>57989</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>47888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63389</t>
+          <t>70790</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -6140,32 +6140,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18246</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>34379</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6175,32 +6175,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18246</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32097</t>
+          <t>34379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -6218,17 +6218,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>396025</t>
+          <t>429286</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>396025</t>
+          <t>429286</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>396025</t>
+          <t>429286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6253,17 +6253,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>396025</t>
+          <t>429286</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>396025</t>
+          <t>429286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>396025</t>
+          <t>429286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6300,32 +6300,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>206164</t>
+          <t>184139</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104670</t>
+          <t>166299</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>287035</t>
+          <t>203026</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6335,32 +6335,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>206164</t>
+          <t>184139</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104670</t>
+          <t>166299</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>287035</t>
+          <t>203026</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -6378,32 +6378,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>433220</t>
+          <t>250187</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>284786</t>
+          <t>228557</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>658121</t>
+          <t>270357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6413,32 +6413,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>433220</t>
+          <t>250187</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>284786</t>
+          <t>228557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>658121</t>
+          <t>270357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -6456,32 +6456,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>173244</t>
+          <t>189271</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94599</t>
+          <t>172091</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>233893</t>
+          <t>209373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6491,32 +6491,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>173244</t>
+          <t>189271</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94599</t>
+          <t>172091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>233893</t>
+          <t>209373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -6534,32 +6534,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>99084</t>
+          <t>106688</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50890</t>
+          <t>92896</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>136645</t>
+          <t>123128</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99084</t>
+          <t>106688</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>50890</t>
+          <t>92896</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>136645</t>
+          <t>123128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -6612,17 +6612,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>911712</t>
+          <t>730286</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>911712</t>
+          <t>730286</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>911712</t>
+          <t>730286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6647,17 +6647,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>911712</t>
+          <t>730286</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>911712</t>
+          <t>730286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>911712</t>
+          <t>730286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6694,32 +6694,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>54335</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44855</t>
+          <t>49440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>66287</t>
+          <t>72137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6729,32 +6729,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54335</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44855</t>
+          <t>49440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66287</t>
+          <t>72137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -6772,32 +6772,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87639</t>
+          <t>97528</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76006</t>
+          <t>83503</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>101217</t>
+          <t>110015</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6807,32 +6807,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87639</t>
+          <t>97528</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76006</t>
+          <t>83503</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>101217</t>
+          <t>110015</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -6850,32 +6850,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>82476</t>
+          <t>93284</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70165</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94291</t>
+          <t>107473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6885,32 +6885,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>82476</t>
+          <t>93284</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70165</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94291</t>
+          <t>107473</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -6928,32 +6928,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43322</t>
+          <t>47513</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>37709</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>43322</t>
+          <t>47513</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34328</t>
+          <t>37709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>59765</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -7006,17 +7006,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>267772</t>
+          <t>298435</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>267772</t>
+          <t>298435</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>267772</t>
+          <t>298435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7041,17 +7041,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>267772</t>
+          <t>298435</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>267772</t>
+          <t>298435</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>267772</t>
+          <t>298435</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7088,32 +7088,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>479333</t>
+          <t>479676</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>304420</t>
+          <t>454388</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>570506</t>
+          <t>508564</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7123,32 +7123,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>479333</t>
+          <t>479676</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>304420</t>
+          <t>454388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>570506</t>
+          <t>508564</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>34,88%</t>
         </is>
       </c>
     </row>
@@ -7166,32 +7166,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>620565</t>
+          <t>457782</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>464730</t>
+          <t>429953</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>959931</t>
+          <t>486774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7201,32 +7201,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>620565</t>
+          <t>457782</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>464730</t>
+          <t>429953</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>959931</t>
+          <t>486774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>33,39%</t>
         </is>
       </c>
     </row>
@@ -7244,32 +7244,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>309114</t>
+          <t>340545</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>199074</t>
+          <t>316989</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>366868</t>
+          <t>367457</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7279,32 +7279,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>309114</t>
+          <t>340545</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>199074</t>
+          <t>316989</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>366868</t>
+          <t>367457</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -7322,32 +7322,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>180005</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107739</t>
+          <t>160531</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>201093</t>
+          <t>200354</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7357,32 +7357,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>166496</t>
+          <t>180005</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107739</t>
+          <t>160531</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>201093</t>
+          <t>200354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -7400,17 +7400,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1575509</t>
+          <t>1458008</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1575509</t>
+          <t>1458008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1575509</t>
+          <t>1458008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7435,17 +7435,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1575509</t>
+          <t>1458008</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1575509</t>
+          <t>1458008</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1575509</t>
+          <t>1458008</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
